--- a/data/raw/male_life_table_central_west_brazil_2025.xlsx
+++ b/data/raw/male_life_table_central_west_brazil_2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/Projeto IC - Vanessa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/projeto_longevidade/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D19A0A5-90F7-4ACC-AD94-4717E5CD616B}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D44B423-8394-4216-8071-833D236FABD6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,31 +516,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>1.3345806958048999E-2</v>
+        <v>1.37946078003664E-2</v>
       </c>
       <c r="C2" s="1">
-        <v>8.0404008561289E-2</v>
+        <v>8.1663372161439804E-2</v>
       </c>
       <c r="D2" s="1">
-        <v>1.3184002977840999E-2</v>
+        <v>1.3622042490935401E-2</v>
       </c>
       <c r="E2" s="2">
         <v>100000</v>
       </c>
       <c r="F2" s="2">
-        <v>1318.4002977841001</v>
+        <v>1362.2042490935401</v>
       </c>
       <c r="G2" s="2">
-        <v>98787.604371046094</v>
+        <v>98749.037943460105</v>
       </c>
       <c r="H2" s="3">
-        <v>0.98587121656460097</v>
+        <v>0.98540336988094102</v>
       </c>
       <c r="I2" s="2">
-        <v>7378488.4514908297</v>
+        <v>7334293.5252832603</v>
       </c>
       <c r="J2" s="4">
-        <v>73.784884514908299</v>
+        <v>73.342935252832604</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -548,31 +548,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>6.1483559359083305E-4</v>
+        <v>6.3620927739141701E-4</v>
       </c>
       <c r="C3" s="1">
-        <v>1.6132544571285701</v>
+        <v>1.61193435401663</v>
       </c>
       <c r="D3" s="1">
-        <v>2.4557386856181702E-3</v>
+        <v>2.5409765796606501E-3</v>
       </c>
       <c r="E3" s="2">
-        <v>98681.599702215899</v>
+        <v>98637.795750906502</v>
       </c>
       <c r="F3" s="2">
-        <v>242.336221947437</v>
+        <v>250.63632887240999</v>
       </c>
       <c r="G3" s="2">
-        <v>394148.003911254</v>
+        <v>393952.64699700999</v>
       </c>
       <c r="H3" s="3">
-        <v>0.99777429993341904</v>
+        <v>0.99769636391944005</v>
       </c>
       <c r="I3" s="2">
-        <v>7279700.8471197803</v>
+        <v>7235544.4873398002</v>
       </c>
       <c r="J3" s="4">
-        <v>73.769586924889694</v>
+        <v>73.354685516411706</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -580,31 +580,31 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>2.7730737781416398E-4</v>
+        <v>2.8629551104544001E-4</v>
       </c>
       <c r="C4" s="1">
-        <v>2.3763854984521098</v>
+        <v>2.3771846493128299</v>
       </c>
       <c r="D4" s="1">
-        <v>1.38552885080058E-3</v>
+        <v>1.43040346489179E-3</v>
       </c>
       <c r="E4" s="2">
-        <v>98439.263480268506</v>
+        <v>98387.159422034005</v>
       </c>
       <c r="F4" s="2">
-        <v>136.39043960346299</v>
+        <v>140.73333373812801</v>
       </c>
       <c r="G4" s="2">
-        <v>491838.48146612599</v>
+        <v>491566.67956208898</v>
       </c>
       <c r="H4" s="3">
-        <v>0.99857105876175001</v>
+        <v>0.99852028763802603</v>
       </c>
       <c r="I4" s="2">
-        <v>6885552.84320853</v>
+        <v>6841591.8403427899</v>
       </c>
       <c r="J4" s="4">
-        <v>69.947220242954103</v>
+        <v>69.537446558403204</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -612,31 +612,31 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>3.5083190218744299E-4</v>
+        <v>3.6438440567247102E-4</v>
       </c>
       <c r="C5" s="1">
-        <v>2.8022129892977898</v>
+        <v>2.8036400628890599</v>
       </c>
       <c r="D5" s="1">
-        <v>1.7528080016711201E-3</v>
+        <v>1.82046507500905E-3</v>
       </c>
       <c r="E5" s="2">
-        <v>98302.873040664999</v>
+        <v>98246.426088295906</v>
       </c>
       <c r="F5" s="2">
-        <v>172.306062452932</v>
+        <v>178.854187438206</v>
       </c>
       <c r="G5" s="2">
-        <v>491135.67317740101</v>
+        <v>490839.30226960598</v>
       </c>
       <c r="H5" s="3">
-        <v>0.99650675959031598</v>
+        <v>0.99637025519572198</v>
       </c>
       <c r="I5" s="2">
-        <v>6393714.3617423996</v>
+        <v>6350025.1607806999</v>
       </c>
       <c r="J5" s="4">
-        <v>65.040971479007695</v>
+        <v>64.633650440106706</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -644,31 +644,31 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>1.1870864537856299E-3</v>
+        <v>1.2341536107740301E-3</v>
       </c>
       <c r="C6" s="1">
-        <v>2.87805350646267</v>
+        <v>2.8789970380076002</v>
       </c>
       <c r="D6" s="1">
-        <v>5.92051887300756E-3</v>
+        <v>6.1546573552709403E-3</v>
       </c>
       <c r="E6" s="2">
-        <v>98130.566978212097</v>
+        <v>98067.5719008577</v>
       </c>
       <c r="F6" s="2">
-        <v>580.98387381344196</v>
+        <v>603.57230271317496</v>
       </c>
       <c r="G6" s="2">
-        <v>489420.01819721999</v>
+        <v>489057.68086245703</v>
       </c>
       <c r="H6" s="3">
-        <v>0.99147384335724198</v>
+        <v>0.99111707300978502</v>
       </c>
       <c r="I6" s="2">
-        <v>5902578.688565</v>
+        <v>5859185.8585110903</v>
       </c>
       <c r="J6" s="4">
-        <v>60.150255627031598</v>
+        <v>59.746415098708603</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -676,31 +676,31 @@
         <v>20</v>
       </c>
       <c r="B7" s="1">
-        <v>2.1794653930504999E-3</v>
+        <v>2.2750030873979099E-3</v>
       </c>
       <c r="C7" s="1">
-        <v>2.6353840174730601</v>
+        <v>2.6362357482258099</v>
       </c>
       <c r="D7" s="1">
-        <v>1.08414544596241E-2</v>
+        <v>1.13141726704797E-2</v>
       </c>
       <c r="E7" s="2">
-        <v>97549.583104398596</v>
+        <v>97463.999598144495</v>
       </c>
       <c r="F7" s="2">
-        <v>1057.5793627816599</v>
+        <v>1102.7245206089699</v>
       </c>
       <c r="G7" s="2">
-        <v>485247.14645796898</v>
+        <v>484713.41718935198</v>
       </c>
       <c r="H7" s="3">
-        <v>0.98854260107213399</v>
+        <v>0.98803495239121497</v>
       </c>
       <c r="I7" s="2">
-        <v>5413158.6703677801</v>
+        <v>5370128.1776486402</v>
       </c>
       <c r="J7" s="4">
-        <v>55.491356273399603</v>
+        <v>55.098582038396799</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -708,31 +708,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="1">
-        <v>2.3236515321988101E-3</v>
+        <v>2.4279979334942301E-3</v>
       </c>
       <c r="C8" s="1">
-        <v>2.51258175913128</v>
+        <v>2.5124070753971699</v>
       </c>
       <c r="D8" s="1">
-        <v>1.15514912750471E-2</v>
+        <v>1.20671059106983E-2</v>
       </c>
       <c r="E8" s="2">
-        <v>96492.003741616994</v>
+        <v>96361.275077535596</v>
       </c>
       <c r="F8" s="2">
-        <v>1114.6265393331</v>
+        <v>1162.8017120505499</v>
       </c>
       <c r="G8" s="2">
-        <v>479687.47632239101</v>
+        <v>478913.79807606502</v>
       </c>
       <c r="H8" s="3">
-        <v>0.98837584275408996</v>
+        <v>0.98786066542034301</v>
       </c>
       <c r="I8" s="2">
-        <v>4927911.52390981</v>
+        <v>4885414.7604592796</v>
       </c>
       <c r="J8" s="4">
-        <v>51.070672520239199</v>
+        <v>50.698942666836999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -740,31 +740,31 @@
         <v>30</v>
       </c>
       <c r="B9" s="1">
-        <v>2.3695701640842402E-3</v>
+        <v>2.47394823647307E-3</v>
       </c>
       <c r="C9" s="1">
-        <v>2.5295778018363402</v>
+        <v>2.52887782595023</v>
       </c>
       <c r="D9" s="1">
-        <v>1.17788990449543E-2</v>
+        <v>1.2294579153682299E-2</v>
       </c>
       <c r="E9" s="2">
-        <v>95377.377202283897</v>
+        <v>95198.473365484999</v>
       </c>
       <c r="F9" s="2">
-        <v>1123.4404972382299</v>
+        <v>1170.4251661016799</v>
       </c>
       <c r="G9" s="2">
-        <v>474111.51366872602</v>
+        <v>473100.10324640502</v>
       </c>
       <c r="H9" s="3">
-        <v>0.987449520415981</v>
+        <v>0.986910499149106</v>
       </c>
       <c r="I9" s="2">
-        <v>4448224.0475874199</v>
+        <v>4406500.96238322</v>
       </c>
       <c r="J9" s="4">
-        <v>46.638146047497997</v>
+        <v>46.287517085130403</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -772,31 +772,31 @@
         <v>35</v>
       </c>
       <c r="B10" s="1">
-        <v>2.7423330469455698E-3</v>
+        <v>2.8588517808973602E-3</v>
       </c>
       <c r="C10" s="1">
-        <v>2.5787768808848801</v>
+        <v>2.5781125232961801</v>
       </c>
       <c r="D10" s="1">
-        <v>1.36212230356514E-2</v>
+        <v>1.41959686110595E-2</v>
       </c>
       <c r="E10" s="2">
-        <v>94253.936705045606</v>
+        <v>94028.048199383295</v>
       </c>
       <c r="F10" s="2">
-        <v>1283.8538938475999</v>
+        <v>1334.8192207976199</v>
       </c>
       <c r="G10" s="2">
-        <v>468161.18679587799</v>
+        <v>466907.45904240297</v>
       </c>
       <c r="H10" s="3">
-        <v>0.98455396299613396</v>
+        <v>0.98390744670507002</v>
       </c>
       <c r="I10" s="2">
-        <v>3974112.5339187002</v>
+        <v>3933400.8591368101</v>
       </c>
       <c r="J10" s="4">
-        <v>42.163889094151301</v>
+        <v>41.832207883292099</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -804,31 +804,31 @@
         <v>40</v>
       </c>
       <c r="B11" s="1">
-        <v>3.5546653793145601E-3</v>
+        <v>3.70374318683343E-3</v>
       </c>
       <c r="C11" s="1">
-        <v>2.60721529056122</v>
+        <v>2.6065380269873</v>
       </c>
       <c r="D11" s="1">
-        <v>1.76234299501687E-2</v>
+        <v>1.8355994294608002E-2</v>
       </c>
       <c r="E11" s="2">
-        <v>92970.082811197994</v>
+        <v>92693.228978585699</v>
       </c>
       <c r="F11" s="2">
-        <v>1638.4517418845201</v>
+        <v>1701.4763822797099</v>
       </c>
       <c r="G11" s="2">
-        <v>460929.951780856</v>
+        <v>459393.72587396298</v>
       </c>
       <c r="H11" s="3">
-        <v>0.97961159838928702</v>
+        <v>0.97877857113509403</v>
       </c>
       <c r="I11" s="2">
-        <v>3505951.3471228201</v>
+        <v>3466493.4000944099</v>
       </c>
       <c r="J11" s="4">
-        <v>37.710532690851103</v>
+        <v>37.397482408291701</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -836,31 +836,31 @@
         <v>45</v>
       </c>
       <c r="B12" s="1">
-        <v>4.7540129053948504E-3</v>
+        <v>4.9472903883701303E-3</v>
       </c>
       <c r="C12" s="1">
-        <v>2.6121069594407298</v>
+        <v>2.6111605920852798</v>
       </c>
       <c r="D12" s="1">
-        <v>2.3503253842323601E-2</v>
+        <v>2.4447524200725001E-2</v>
       </c>
       <c r="E12" s="2">
-        <v>91331.631069313502</v>
+        <v>90991.752596306003</v>
       </c>
       <c r="F12" s="2">
-        <v>2146.5905088555301</v>
+        <v>2224.5230736645899</v>
       </c>
       <c r="G12" s="2">
-        <v>451532.32680954097</v>
+        <v>449644.73459934402</v>
       </c>
       <c r="H12" s="3">
-        <v>0.97288700806738404</v>
+        <v>0.97181922707961499</v>
       </c>
       <c r="I12" s="2">
-        <v>3045021.3953419598</v>
+        <v>3007099.6742204502</v>
       </c>
       <c r="J12" s="4">
-        <v>33.340271707520799</v>
+        <v>33.048046536280502</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -868,31 +868,31 @@
         <v>50</v>
       </c>
       <c r="B13" s="1">
-        <v>6.3847636121049196E-3</v>
+        <v>6.6351928058217902E-3</v>
       </c>
       <c r="C13" s="1">
-        <v>2.6342850455564002</v>
+        <v>2.6330472973212098</v>
       </c>
       <c r="D13" s="1">
-        <v>3.1448798713068903E-2</v>
+        <v>3.2662985712726099E-2</v>
       </c>
       <c r="E13" s="2">
-        <v>89185.040560458001</v>
+        <v>88767.229522641399</v>
       </c>
       <c r="F13" s="2">
-        <v>2804.7623888027301</v>
+        <v>2899.4027496563199</v>
       </c>
       <c r="G13" s="2">
-        <v>439289.93447543803</v>
+        <v>436973.39843875403</v>
       </c>
       <c r="H13" s="3">
-        <v>0.96135921284557202</v>
+        <v>0.95991725830654195</v>
       </c>
       <c r="I13" s="2">
-        <v>2593489.0685324199</v>
+        <v>2557454.9396211002</v>
       </c>
       <c r="J13" s="4">
-        <v>29.079866446596601</v>
+        <v>28.810800487682101</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -900,31 +900,31 @@
         <v>55</v>
       </c>
       <c r="B14" s="1">
-        <v>9.6543147364105894E-3</v>
+        <v>1.00123465418035E-2</v>
       </c>
       <c r="C14" s="1">
-        <v>2.6488656206081602</v>
+        <v>2.6472887134176202</v>
       </c>
       <c r="D14" s="1">
-        <v>4.72001957305348E-2</v>
+        <v>4.8909610073659703E-2</v>
       </c>
       <c r="E14" s="2">
-        <v>86380.2781716553</v>
+        <v>85867.826772985107</v>
       </c>
       <c r="F14" s="2">
-        <v>4077.16603696017</v>
+        <v>4199.7619253392504</v>
       </c>
       <c r="G14" s="2">
-        <v>422315.42561829003</v>
+        <v>419458.306582221</v>
       </c>
       <c r="H14" s="3">
-        <v>0.942453080343848</v>
+        <v>0.94043828471315305</v>
       </c>
       <c r="I14" s="2">
-        <v>2154199.1340569798</v>
+        <v>2120481.5411823499</v>
       </c>
       <c r="J14" s="4">
-        <v>24.9385528693963</v>
+        <v>24.6947153651439</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -932,31 +932,31 @@
         <v>60</v>
       </c>
       <c r="B15" s="1">
-        <v>1.4368130478452E-2</v>
+        <v>1.4872249341112E-2</v>
       </c>
       <c r="C15" s="1">
-        <v>2.6387818274905701</v>
+        <v>2.63655650478964</v>
       </c>
       <c r="D15" s="1">
-        <v>6.9483340381371703E-2</v>
+        <v>7.1836223494588999E-2</v>
       </c>
       <c r="E15" s="2">
-        <v>82303.112134695097</v>
+        <v>81668.064847645801</v>
       </c>
       <c r="F15" s="2">
-        <v>5718.6951549012301</v>
+        <v>5866.7253587660798</v>
       </c>
       <c r="G15" s="2">
-        <v>398012.47375068098</v>
+        <v>394474.650350868</v>
       </c>
       <c r="H15" s="3">
-        <v>0.914621159211785</v>
+        <v>0.91191751115986397</v>
       </c>
       <c r="I15" s="2">
-        <v>1731883.7084386901</v>
+        <v>1701023.23460013</v>
       </c>
       <c r="J15" s="4">
-        <v>21.042748731109199</v>
+        <v>20.828499337818698</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -964,31 +964,31 @@
         <v>65</v>
       </c>
       <c r="B16" s="1">
-        <v>2.1698410632119799E-2</v>
+        <v>2.2376531349431999E-2</v>
       </c>
       <c r="C16" s="1">
-        <v>2.60833938494652</v>
+        <v>2.6050162216106099</v>
       </c>
       <c r="D16" s="1">
-        <v>0.103139599497813</v>
+        <v>0.106191692153186</v>
       </c>
       <c r="E16" s="2">
-        <v>76584.416979793896</v>
+        <v>75801.339488879807</v>
       </c>
       <c r="F16" s="2">
-        <v>7898.8860950694498</v>
+        <v>8049.4725078022702</v>
       </c>
       <c r="G16" s="2">
-        <v>364030.63012259803</v>
+        <v>359728.341363621</v>
       </c>
       <c r="H16" s="3">
-        <v>0.88010202426709205</v>
+        <v>0.87693145815951101</v>
       </c>
       <c r="I16" s="2">
-        <v>1333871.2346880101</v>
+        <v>1306548.5842492599</v>
       </c>
       <c r="J16" s="4">
-        <v>17.417005799495001</v>
+        <v>17.2364841183438</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -996,31 +996,31 @@
         <v>70</v>
       </c>
       <c r="B17" s="1">
-        <v>3.00248612488235E-2</v>
+        <v>3.07946259715557E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>2.60449204791361</v>
+        <v>2.6012645290576399</v>
       </c>
       <c r="D17" s="1">
-        <v>0.14005115573496599</v>
+        <v>0.143381781264216</v>
       </c>
       <c r="E17" s="2">
-        <v>68685.530884724401</v>
+        <v>67751.866981077503</v>
       </c>
       <c r="F17" s="2">
-        <v>9619.4879826753404</v>
+        <v>9714.38337172309</v>
       </c>
       <c r="G17" s="2">
-        <v>320384.09446612402</v>
+        <v>315457.09893330297</v>
       </c>
       <c r="H17" s="3">
-        <v>0.825825047888186</v>
+        <v>0.82199117823808698</v>
       </c>
       <c r="I17" s="2">
-        <v>969840.60456541402</v>
+        <v>946820.24288563896</v>
       </c>
       <c r="J17" s="4">
-        <v>14.1200132265572</v>
+        <v>13.974821434073201</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1028,31 +1028,31 @@
         <v>75</v>
       </c>
       <c r="B18" s="1">
-        <v>4.83782076701329E-2</v>
+        <v>4.9502773643620601E-2</v>
       </c>
       <c r="C18" s="1">
-        <v>2.5977274154607701</v>
+        <v>2.5939585971467101</v>
       </c>
       <c r="D18" s="1">
-        <v>0.21670598031638999</v>
+        <v>0.22117112185547499</v>
       </c>
       <c r="E18" s="2">
-        <v>59066.042902049099</v>
+        <v>58037.4836093544</v>
       </c>
       <c r="F18" s="2">
-        <v>12799.964730498499</v>
+        <v>12836.2153595497</v>
       </c>
       <c r="G18" s="2">
-        <v>264581.21015509998</v>
+        <v>259302.95243575401</v>
       </c>
       <c r="H18" s="3">
-        <v>0.73416140749943004</v>
+        <v>0.72948533406937999</v>
       </c>
       <c r="I18" s="2">
-        <v>649456.51009929006</v>
+        <v>631363.14395233605</v>
       </c>
       <c r="J18" s="4">
-        <v>10.995429491972301</v>
+        <v>10.8785409822726</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1060,31 +1060,31 @@
         <v>80</v>
       </c>
       <c r="B19" s="1">
-        <v>7.7858993704764803E-2</v>
+        <v>7.9310394326974107E-2</v>
       </c>
       <c r="C19" s="1">
-        <v>2.54789054794343</v>
+        <v>2.5437796112415398</v>
       </c>
       <c r="D19" s="1">
-        <v>0.32688624690031998</v>
+        <v>0.331897144214783</v>
       </c>
       <c r="E19" s="2">
-        <v>46266.078171550602</v>
+        <v>45201.2682498047</v>
       </c>
       <c r="F19" s="2">
-        <v>15123.744652294999</v>
+        <v>15002.1718469965</v>
       </c>
       <c r="G19" s="2">
-        <v>194245.31364537001</v>
+        <v>189157.700882773</v>
       </c>
       <c r="H19" s="3">
-        <v>0.59795162357941101</v>
+        <v>0.59229750814105098</v>
       </c>
       <c r="I19" s="2">
-        <v>384875.29994419002</v>
+        <v>372060.19151658198</v>
       </c>
       <c r="J19" s="4">
-        <v>8.3187362135408698</v>
+        <v>8.2311892104529498</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1092,31 +1092,31 @@
         <v>85</v>
       </c>
       <c r="B20" s="1">
-        <v>0.132623465248525</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="C20" s="1">
-        <v>2.4317026944380999</v>
+        <v>2.4242883138256501</v>
       </c>
       <c r="D20" s="1">
-        <v>0.494636111038949</v>
+        <v>0.50084547255522105</v>
       </c>
       <c r="E20" s="2">
-        <v>31142.333519255601</v>
+        <v>30199.096402808202</v>
       </c>
       <c r="F20" s="2">
-        <v>15404.122740642501</v>
+        <v>15125.080708605199</v>
       </c>
       <c r="G20" s="2">
-        <v>116149.300666941</v>
+        <v>112037.634878557</v>
       </c>
       <c r="H20" s="3">
-        <v>0.39070813085580097</v>
+        <v>0.38744609496396598</v>
       </c>
       <c r="I20" s="2">
-        <v>190629.98629882</v>
+        <v>182902.49063381</v>
       </c>
       <c r="J20" s="4">
-        <v>6.1212492692929299</v>
+        <v>6.0565550768201604</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1124,31 +1124,31 @@
         <v>90</v>
       </c>
       <c r="B21" s="1">
-        <v>0.21130593314351701</v>
+        <v>0.21271497039751899</v>
       </c>
       <c r="C21" s="1">
-        <v>4.7324747825268503</v>
+        <v>4.7011265738899901</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="E21" s="2">
-        <v>15738.2107786131</v>
+        <v>15074.015694203101</v>
       </c>
       <c r="F21" s="2">
-        <v>15738.2107786131</v>
+        <v>15074.015694203101</v>
       </c>
       <c r="G21" s="2">
-        <v>74480.685631878805</v>
+        <v>70864.855755252895</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>74480.685631878805</v>
+        <v>70864.855755252895</v>
       </c>
       <c r="J21" s="4">
-        <v>4.7324747825268503</v>
+        <v>4.7011265738899901</v>
       </c>
     </row>
   </sheetData>
